--- a/models/plantilla_informe_he.xlsx
+++ b/models/plantilla_informe_he.xlsx
@@ -1,49 +1,33 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
-  <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\192.168.122.1\SharedVM\[ 09 ] epalacios\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1AEEF6FB-0BE0-41BB-AA5B-A2C9A6E95DEF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2">
+  <fileVersion appName="Calc" lowestEdited="7"/>
+  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="26820" windowHeight="15240" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="HORAS_EXTRA" sheetId="1" r:id="rId1"/>
+    <sheet name="HORAS_EXTRA" sheetId="1" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_Fill">NA()</definedName>
-    <definedName name="_Key1">NA()</definedName>
-    <definedName name="_Order1">255</definedName>
-    <definedName name="_Regression_Int" localSheetId="0">1</definedName>
-    <definedName name="_Sort">NA()</definedName>
-    <definedName name="_xlfn__FV">#REF!</definedName>
-    <definedName name="_xlfn_IFERROR">#REF!</definedName>
-    <definedName name="AREA">NA()</definedName>
-    <definedName name="AREA_2000">NA()</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">HORAS_EXTRA!$A$1:$J$36</definedName>
-    <definedName name="Imprimir_área_IM" localSheetId="0">NA()</definedName>
-    <definedName name="Imprimir_títulos_IM" localSheetId="0">NA()</definedName>
-    <definedName name="LISTAMAT">NA()</definedName>
-    <definedName name="Listamateriales">NA()</definedName>
+    <definedName function="false" hidden="false" localSheetId="0" name="_xlnm.Print_Area" vbProcedure="false">HORAS_EXTRA!$A$1:$J$36</definedName>
+    <definedName function="false" hidden="false" name="AREA" vbProcedure="false">NA()</definedName>
+    <definedName function="false" hidden="false" name="AREA_2000" vbProcedure="false">NA()</definedName>
+    <definedName function="false" hidden="false" name="LISTAMAT" vbProcedure="false">NA()</definedName>
+    <definedName function="false" hidden="false" name="Listamateriales" vbProcedure="false">NA()</definedName>
+    <definedName function="false" hidden="false" name="_Fill" vbProcedure="false">NA()</definedName>
+    <definedName function="false" hidden="false" name="_Key1" vbProcedure="false">NA()</definedName>
+    <definedName function="false" hidden="false" name="_Order1" vbProcedure="false">255</definedName>
+    <definedName function="false" hidden="false" name="_Sort" vbProcedure="false">NA()</definedName>
+    <definedName function="false" hidden="false" name="_xlfn_IFERROR" vbProcedure="false">#ref!</definedName>
+    <definedName function="false" hidden="false" name="_xlfn__FV" vbProcedure="false">#ref!</definedName>
+    <definedName function="false" hidden="false" localSheetId="0" name="Imprimir_títulos_IM" vbProcedure="false">NA()</definedName>
+    <definedName function="false" hidden="false" localSheetId="0" name="Imprimir_área_IM" vbProcedure="false">NA()</definedName>
+    <definedName function="false" hidden="false" localSheetId="0" name="_Regression_Int" vbProcedure="false">1</definedName>
   </definedNames>
-  <calcPr calcId="191029" iterateDelta="1E-4"/>
+  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
       <loext:extCalcPr stringRefSyntax="CalcA1ExcelA1"/>
     </ext>
@@ -56,7 +40,7 @@
   <si>
     <r>
       <rPr>
-        <b/>
+        <b val="true"/>
         <sz val="12"/>
         <rFont val="Franklin Gothic Book"/>
         <family val="2"/>
@@ -81,107 +65,128 @@
     <t xml:space="preserve">Nombre del trabajador: </t>
   </si>
   <si>
-    <t>HOJA DE PRUEBA</t>
-  </si>
-  <si>
-    <t>TOTAL</t>
-  </si>
-  <si>
-    <t>Cuadrilla o Agencia:</t>
-  </si>
-  <si>
-    <t>AGENCIA GUALAQUIZA</t>
-  </si>
-  <si>
-    <t>( horas reloj )</t>
-  </si>
-  <si>
-    <t>Parte:</t>
+    <t xml:space="preserve">HOJA DE PRUEBA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TOTAL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cuadrilla o Agencia:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AGENCIA GUALAQUIZA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">( horas reloj )</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Parte:</t>
   </si>
   <si>
     <t xml:space="preserve">                      Trabajador                                                         Jefe Zonal                                                          Ingeniero 1                            </t>
   </si>
   <si>
-    <t>DIA</t>
-  </si>
-  <si>
-    <t>FECHA</t>
-  </si>
-  <si>
-    <t>Extra 1</t>
-  </si>
-  <si>
-    <t>Fin 1</t>
-  </si>
-  <si>
-    <t>Extra 2</t>
-  </si>
-  <si>
-    <t>Fin 2</t>
-  </si>
-  <si>
-    <t>Extra 3</t>
-  </si>
-  <si>
-    <t>Fin 3</t>
-  </si>
-  <si>
-    <t>Horas</t>
-  </si>
-  <si>
-    <t>BREVE EXPLICACION</t>
-  </si>
-  <si>
-    <t>OT # 173960. Guayusal, reivision y limpieza RBV rehabilitacion de trafo # 23459.</t>
-  </si>
-  <si>
-    <t>OT # 174080. FESTIVO. Naichap, restitución M# 194238 por 18-258039. Aguacate, restitución M# 194324 por 18-258040.</t>
-  </si>
-  <si>
-    <t>OT # 174310. La Pradera, se arregla acometida M# 240908, se rehabilita trafo # 20916</t>
-  </si>
-  <si>
-    <t>OT # 174313. Shiramentza, Est 22357 cambi0 tirafusible de 1.3A-SR</t>
-  </si>
-  <si>
-    <t>OT # 174486.Tutus, Est 91980 cambio de tirafusible 12A-T</t>
+    <t xml:space="preserve">DÍA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FECHA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extra 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fin 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extra 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fin 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extra 3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fin 3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Horas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BREVE EXPLICACIÓN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OT # 173960. Guayusal, reivision y limpieza RBV rehabilitacion de trafo # 23459.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OT # 174080. FESTIVO. Naichap, restitución M# 194238 por 18-258039. Aguacate, restitución M# 194324 por 18-258040.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OT # 174310. La Pradera, se arregla acometida M# 240908, se rehabilita trafo # 20916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OT # 174313. Shiramentza, Est 22357 cambi0 tirafusible de 1.3A-SR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OT # 174486.Tutus, Est 91980 cambio de tirafusible 12A-T</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="3">
-    <numFmt numFmtId="164" formatCode="&quot;( &quot;[h]:mm&quot; )&quot;"/>
-    <numFmt numFmtId="165" formatCode="h:mm;@"/>
-    <numFmt numFmtId="166" formatCode="[$-C0A]d/mmm\ yyyy;@"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="5">
+    <numFmt numFmtId="164" formatCode="General"/>
+    <numFmt numFmtId="165" formatCode="0.00"/>
+    <numFmt numFmtId="166" formatCode="&quot;( &quot;[h]:mm&quot; )&quot;"/>
+    <numFmt numFmtId="167" formatCode="h:mm;@"/>
+    <numFmt numFmtId="168" formatCode="[$-C0A]d/mmm\ yyyy;@"/>
   </numFmts>
-  <fonts count="21">
+  <fonts count="24">
     <font>
       <sz val="12"/>
       <name val="Courier New"/>
+      <family val="0"/>
       <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="0"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="0"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="0"/>
     </font>
     <font>
       <sz val="1"/>
       <color rgb="FF000000"/>
       <name val="Courier New"/>
+      <family val="0"/>
       <charset val="134"/>
     </font>
     <font>
-      <i/>
+      <i val="true"/>
       <sz val="1"/>
       <color rgb="FF000000"/>
       <name val="Courier New"/>
+      <family val="0"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="Arial"/>
+      <family val="0"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
+      <b val="true"/>
       <sz val="12"/>
       <name val="Franklin Gothic Book"/>
       <family val="2"/>
@@ -194,7 +199,7 @@
       <charset val="1"/>
     </font>
     <font>
-      <b/>
+      <b val="true"/>
       <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
@@ -208,14 +213,14 @@
       <charset val="1"/>
     </font>
     <font>
-      <b/>
+      <b val="true"/>
       <sz val="18"/>
       <name val="Calibri"/>
       <family val="2"/>
       <charset val="1"/>
     </font>
     <font>
-      <b/>
+      <b val="true"/>
       <sz val="18"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
@@ -223,14 +228,14 @@
       <charset val="1"/>
     </font>
     <font>
-      <b/>
+      <b val="true"/>
       <sz val="12"/>
       <name val="Calibri"/>
       <family val="2"/>
       <charset val="1"/>
     </font>
     <font>
-      <b/>
+      <b val="true"/>
       <sz val="21"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -244,9 +249,10 @@
       <charset val="1"/>
     </font>
     <font>
-      <b/>
+      <b val="true"/>
       <sz val="21"/>
       <name val="Times New Roman"/>
+      <family val="0"/>
       <charset val="134"/>
     </font>
     <font>
@@ -256,7 +262,7 @@
       <charset val="1"/>
     </font>
     <font>
-      <b/>
+      <b val="true"/>
       <sz val="12"/>
       <color theme="0"/>
       <name val="Calibri"/>
@@ -264,7 +270,7 @@
       <charset val="1"/>
     </font>
     <font>
-      <b/>
+      <b val="true"/>
       <sz val="12"/>
       <color theme="0"/>
       <name val="Aptos Display"/>
@@ -287,6 +293,7 @@
     <font>
       <sz val="9"/>
       <name val="Iosevka Aile"/>
+      <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
@@ -311,139 +318,123 @@
     </fill>
   </fills>
   <borders count="17">
-    <border>
+    <border diagonalUp="false" diagonalDown="false">
       <left/>
       <right/>
       <top/>
       <bottom/>
       <diagonal/>
     </border>
-    <border>
+    <border diagonalUp="false" diagonalDown="false">
+      <left style="thin"/>
+      <right style="thin">
+        <color rgb="FF3465A4"/>
+      </right>
+      <top style="thin"/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border diagonalUp="false" diagonalDown="false">
+      <left/>
+      <right style="thin">
+        <color rgb="FF3465A4"/>
+      </right>
+      <top style="thin"/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border diagonalUp="false" diagonalDown="false">
+      <left/>
+      <right/>
+      <top style="thin"/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border diagonalUp="false" diagonalDown="false">
+      <left/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border diagonalUp="false" diagonalDown="false">
+      <left style="thin"/>
+      <right/>
+      <top style="hair">
+        <color rgb="FF3465A4"/>
+      </top>
+      <bottom style="hair">
+        <color rgb="FF3465A4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border diagonalUp="false" diagonalDown="false">
+      <left/>
+      <right style="thin">
+        <color rgb="FF3465A4"/>
+      </right>
+      <top/>
+      <bottom style="hair">
+        <color rgb="FF3465A4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border diagonalUp="false" diagonalDown="false">
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="hair">
+        <color rgb="FF3465A4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border diagonalUp="false" diagonalDown="false">
       <left style="thin">
-        <color auto="1"/>
+        <color rgb="FF3465A4"/>
       </left>
+      <right style="thin"/>
+      <top style="hair">
+        <color rgb="FF3465A4"/>
+      </top>
+      <bottom style="hair">
+        <color rgb="FF3465A4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border diagonalUp="false" diagonalDown="false">
+      <left/>
       <right style="thin">
         <color rgb="FF3465A4"/>
       </right>
-      <top style="thin">
-        <color auto="1"/>
+      <top style="hair">
+        <color rgb="FF3465A4"/>
+      </top>
+      <bottom style="hair">
+        <color rgb="FF3465A4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border diagonalUp="false" diagonalDown="false">
+      <left/>
+      <right/>
+      <top style="hair">
+        <color rgb="FF3465A4"/>
+      </top>
+      <bottom style="hair">
+        <color rgb="FF3465A4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border diagonalUp="false" diagonalDown="false">
+      <left/>
+      <right/>
+      <top style="hair">
+        <color rgb="FF3465A4"/>
       </top>
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="FF3465A4"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right/>
-      <top style="hair">
-        <color rgb="FF3465A4"/>
-      </top>
-      <bottom style="hair">
-        <color rgb="FF3465A4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="FF3465A4"/>
-      </right>
-      <top/>
-      <bottom style="hair">
-        <color rgb="FF3465A4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="hair">
-        <color rgb="FF3465A4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3465A4"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="hair">
-        <color rgb="FF3465A4"/>
-      </top>
-      <bottom style="hair">
-        <color rgb="FF3465A4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="FF3465A4"/>
-      </right>
-      <top style="hair">
-        <color rgb="FF3465A4"/>
-      </top>
-      <bottom style="hair">
-        <color rgb="FF3465A4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="hair">
-        <color rgb="FF3465A4"/>
-      </top>
-      <bottom style="hair">
-        <color rgb="FF3465A4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="hair">
-        <color rgb="FF3465A4"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
+    <border diagonalUp="false" diagonalDown="false">
       <left style="thin">
         <color rgb="FF3465A4"/>
       </left>
@@ -458,239 +449,303 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
+    <border diagonalUp="false" diagonalDown="false">
+      <left style="thin"/>
       <right/>
       <top style="hair">
         <color rgb="FF3465A4"/>
       </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
+      <bottom style="thin"/>
       <diagonal/>
     </border>
-    <border>
+    <border diagonalUp="false" diagonalDown="false">
       <left/>
       <right style="thin">
         <color rgb="FF3465A4"/>
       </right>
       <top/>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
+      <bottom style="thin"/>
       <diagonal/>
     </border>
-    <border>
+    <border diagonalUp="false" diagonalDown="false">
       <left/>
       <right/>
       <top/>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
+      <bottom style="thin"/>
       <diagonal/>
     </border>
-    <border>
+    <border diagonalUp="false" diagonalDown="false">
       <left style="thin">
         <color rgb="FF3465A4"/>
       </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
+      <right style="thin"/>
       <top/>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
+      <bottom style="thin"/>
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="9">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
+  <cellStyleXfs count="28">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="false" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="false" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="false" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="false" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="false" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="false" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="false" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
   </cellStyleXfs>
   <cellXfs count="45">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="165" fontId="18" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="7" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="7" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="7" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="7" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="7" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="7" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="7" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="7" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="18" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="7" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="7" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="7" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="true"/>
+    </xf>
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="true"/>
+    </xf>
+    <xf numFmtId="164" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="18" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="18" fillId="2" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="18" fillId="2" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="18" fillId="2" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="21" fillId="0" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="10" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="22" fillId="0" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="10" fillId="0" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="10" fillId="0" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="10" fillId="0" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="10" fillId="0" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="10" fillId="0" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="21" fillId="0" borderId="13" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="10" fillId="0" borderId="14" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="10" fillId="0" borderId="15" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="10" fillId="0" borderId="14" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="22" fillId="0" borderId="16" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
-  <cellStyles count="9">
-    <cellStyle name="F2" xfId="1" xr:uid="{00000000-0005-0000-0000-000006000000}"/>
-    <cellStyle name="F3" xfId="2" xr:uid="{00000000-0005-0000-0000-000007000000}"/>
-    <cellStyle name="F4" xfId="3" xr:uid="{00000000-0005-0000-0000-000008000000}"/>
-    <cellStyle name="F5" xfId="4" xr:uid="{00000000-0005-0000-0000-000009000000}"/>
-    <cellStyle name="F6" xfId="5" xr:uid="{00000000-0005-0000-0000-00000A000000}"/>
-    <cellStyle name="F7" xfId="6" xr:uid="{00000000-0005-0000-0000-00000B000000}"/>
-    <cellStyle name="F8" xfId="7" xr:uid="{00000000-0005-0000-0000-00000C000000}"/>
+  <cellStyles count="14">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Normal 2" xfId="8" xr:uid="{00000000-0005-0000-0000-00000D000000}"/>
+    <cellStyle name="Comma" xfId="15" builtinId="3"/>
+    <cellStyle name="Comma [0]" xfId="16" builtinId="6"/>
+    <cellStyle name="Currency" xfId="17" builtinId="4"/>
+    <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
+    <cellStyle name="Percent" xfId="19" builtinId="5"/>
+    <cellStyle name="F2" xfId="20"/>
+    <cellStyle name="F3" xfId="21"/>
+    <cellStyle name="F4" xfId="22"/>
+    <cellStyle name="F5" xfId="23"/>
+    <cellStyle name="F6" xfId="24"/>
+    <cellStyle name="F7" xfId="25"/>
+    <cellStyle name="F8" xfId="26"/>
+    <cellStyle name="Normal 2" xfId="27"/>
   </cellStyles>
-  <dxfs count="4">
+  <dxfs count="1">
     <dxf>
       <font>
-        <color theme="2" tint="-0.24994659260841701"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="2" tint="-0.24994659260841701"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="2" tint="-0.24994659260841701"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="2" tint="-0.24994659260841701"/>
+        <color rgb="FFBFBFBF"/>
       </font>
     </dxf>
   </dxfs>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="FF000000"/>
@@ -707,7 +762,7 @@
       <rgbColor rgb="FF808000"/>
       <rgbColor rgb="FF800080"/>
       <rgbColor rgb="FF008080"/>
-      <rgbColor rgb="FFC0C0C0"/>
+      <rgbColor rgb="FFBFBFBF"/>
       <rgbColor rgb="FF808080"/>
       <rgbColor rgb="FF9999FF"/>
       <rgbColor rgb="FF993366"/>
@@ -749,29 +804,13 @@
       <rgbColor rgb="FF993366"/>
       <rgbColor rgb="FF333399"/>
       <rgbColor rgb="FF333333"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
     </indexedColors>
   </colors>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>0</xdr:col>
@@ -781,29 +820,23 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>108720</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>1053720</xdr:rowOff>
+      <xdr:colOff>108360</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>86760</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Imagen 2">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
+        <xdr:cNvPr id="1" name="Imagen 2"/>
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:blip r:embed="rId1"/>
         <a:stretch/>
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
           <a:off x="0" y="0"/>
-          <a:ext cx="2037960" cy="1053720"/>
+          <a:ext cx="2037600" cy="1053360"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -825,29 +858,23 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>7869600</xdr:colOff>
+      <xdr:colOff>7869240</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>399240</xdr:rowOff>
+      <xdr:rowOff>398880</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="Imagen 4">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000003000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
+        <xdr:cNvPr id="2" name="Imagen 4"/>
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:blip r:embed="rId2"/>
         <a:stretch/>
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="10010520" y="21960"/>
-          <a:ext cx="4149360" cy="377280"/>
+          <a:off x="10009800" y="21960"/>
+          <a:ext cx="4149000" cy="376920"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -864,7 +891,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office">
   <a:themeElements>
     <a:clrScheme name="LibreOffice">
       <a:dk1>
@@ -906,14 +933,14 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Arial"/>
-        <a:ea typeface="DejaVu Sans"/>
-        <a:cs typeface="DejaVu Sans"/>
+        <a:latin typeface="Arial" pitchFamily="0" charset="1"/>
+        <a:ea typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
+        <a:cs typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Arial"/>
-        <a:ea typeface="DejaVu Sans"/>
-        <a:cs typeface="DejaVu Sans"/>
+        <a:latin typeface="Arial" pitchFamily="0" charset="1"/>
+        <a:ea typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
+        <a:cs typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme>
@@ -966,42 +993,43 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
   <dimension ref="A1:N37"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.8984375" defaultRowHeight="15.75"/>
+  <sheetFormatPr defaultColWidth="8.8984375" defaultRowHeight="15.75" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="1" width="9.296875" customWidth="1"/>
-    <col min="2" max="2" width="11.796875" customWidth="1"/>
-    <col min="3" max="8" width="6.296875" customWidth="1"/>
-    <col min="9" max="9" width="9.8984375" style="2" customWidth="1"/>
-    <col min="10" max="10" width="101.59765625" customWidth="1"/>
-    <col min="11" max="11" width="7.8984375" hidden="1" customWidth="1"/>
-    <col min="12" max="12" width="8.59765625" customWidth="1"/>
-    <col min="13" max="13" width="12.19921875" customWidth="1"/>
-    <col min="14" max="14" width="3.296875" customWidth="1"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="9.3"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="11.8"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="3" style="0" width="6.3"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="9.9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="101.6"/>
+    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="11" min="11" style="0" width="7.9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="8.6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="12.2"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="0" width="3.3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="84.75" customHeight="1">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
-      <c r="H1" s="1"/>
-      <c r="I1" s="1"/>
-      <c r="J1" s="1"/>
-    </row>
-    <row r="2" spans="1:14" ht="21.75" customHeight="1">
+    <row r="1" customFormat="false" ht="76.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+      <c r="G1" s="2"/>
+      <c r="H1" s="2"/>
+      <c r="I1" s="2"/>
+      <c r="J1" s="2"/>
+    </row>
+    <row r="2" customFormat="false" ht="18.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
@@ -1014,15 +1042,15 @@
       <c r="H2" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="I2" s="7" t="e">
-        <f ca="1">SUM(K6:K36)</f>
-        <v>#VALUE!</v>
+      <c r="I2" s="7" t="n">
+        <f aca="false">SUM(K6:K36)</f>
+        <v>52.5166666666667</v>
       </c>
       <c r="J2" s="8" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:14" ht="18.75" customHeight="1">
+    <row r="3" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="9" t="s">
         <v>4</v>
       </c>
@@ -1035,9 +1063,9 @@
       <c r="H3" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="I3" s="11">
-        <f>SUM(I6:I36)</f>
-        <v>1.318750000000001</v>
+      <c r="I3" s="11" t="n">
+        <f aca="false">SUM(I6:I36)</f>
+        <v>1.31875</v>
       </c>
       <c r="J3" s="12" t="s">
         <v>6</v>
@@ -1047,7 +1075,7 @@
       <c r="M3" s="13"/>
       <c r="N3" s="13"/>
     </row>
-    <row r="4" spans="1:14" s="20" customFormat="1" ht="22.5" customHeight="1">
+    <row r="4" s="20" customFormat="true" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="14" t="s">
         <v>7</v>
       </c>
@@ -1058,7 +1086,7 @@
       <c r="F4" s="15"/>
       <c r="G4" s="15"/>
       <c r="H4" s="16" t="str">
-        <f>UPPER(TEXT(B6, "mmmm aaaa"))</f>
+        <f aca="false">UPPER(TEXT(B6, "mmmm aaaa"))</f>
         <v>MAYO 2026</v>
       </c>
       <c r="I4" s="17"/>
@@ -1070,7 +1098,7 @@
       <c r="M4" s="19"/>
       <c r="N4" s="19"/>
     </row>
-    <row r="5" spans="1:14" s="26" customFormat="1">
+    <row r="5" s="26" customFormat="true" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="21" t="s">
         <v>9</v>
       </c>
@@ -1106,12 +1134,12 @@
       <c r="M5" s="25"/>
       <c r="N5" s="25"/>
     </row>
-    <row r="6" spans="1:14" ht="18.75">
+    <row r="6" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="27" t="str">
-        <f t="shared" ref="A6:A36" si="0">IF(B6&gt;0,PROPER(TEXT(B6,"dddd")),"")</f>
+        <f aca="false">IF(B6&gt;0,PROPER(TEXT(B6,"dddd")),"")</f>
         <v>Viernes</v>
       </c>
-      <c r="B6" s="28">
+      <c r="B6" s="28" t="n">
         <v>46143</v>
       </c>
       <c r="C6" s="29"/>
@@ -1120,201 +1148,201 @@
       <c r="F6" s="30"/>
       <c r="G6" s="29"/>
       <c r="H6" s="30"/>
-      <c r="I6" s="29">
+      <c r="I6" s="29" t="n">
         <v>0</v>
       </c>
       <c r="J6" s="31" t="s">
         <v>19</v>
       </c>
-      <c r="K6" t="e">
-        <f t="array" aca="1" ref="K6" ca="1">SUM((INDIRECT("D"&amp;ROW())-INDIRECT("C"&amp;ROW()))*2*24,(INDIRECT("F"&amp;ROW())-INDIRECT("E"&amp;ROW()))*2*24,(INDIRECT("H"&amp;ROW())-INDIRECT("G"&amp;ROW()))*2*24)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="7" spans="1:14" ht="18.75">
+      <c r="K6" s="0" t="n">
+        <f aca="true" t="array" ref="K6">SUM((INDIRECT("D"&amp;ROW())-INDIRECT("C"&amp;ROW()))*2*24,(INDIRECT("F"&amp;ROW())-INDIRECT("E"&amp;ROW()))*2*24,(INDIRECT("H"&amp;ROW())-INDIRECT("G"&amp;ROW()))*2*24)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="27" t="str">
-        <f t="shared" si="0"/>
+        <f aca="false">IF(B7&gt;0,PROPER(TEXT(B7,"dddd")),"")</f>
         <v>Sábado</v>
       </c>
-      <c r="B7" s="32">
+      <c r="B7" s="32" t="n">
         <v>46144</v>
       </c>
-      <c r="C7" s="33">
-        <v>0.80347222222222203</v>
-      </c>
-      <c r="D7" s="34">
-        <v>0.86527777777777803</v>
+      <c r="C7" s="33" t="n">
+        <v>0.803472222222222</v>
+      </c>
+      <c r="D7" s="34" t="n">
+        <v>0.865277777777778</v>
       </c>
       <c r="E7" s="33"/>
       <c r="F7" s="34"/>
       <c r="G7" s="33"/>
       <c r="H7" s="34"/>
-      <c r="I7" s="33">
-        <v>6.18055555555556E-2</v>
+      <c r="I7" s="33" t="n">
+        <v>0.0618055555555556</v>
       </c>
       <c r="J7" s="31" t="s">
         <v>19</v>
       </c>
-      <c r="K7" t="e">
-        <f t="array" aca="1" ref="K7" ca="1">SUM((INDIRECT("D"&amp;ROW())-INDIRECT("C"&amp;ROW()))*2*24,(INDIRECT("F"&amp;ROW())-INDIRECT("E"&amp;ROW()))*2*24,(INDIRECT("H"&amp;ROW())-INDIRECT("G"&amp;ROW()))*2*24)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14" ht="18.75">
+      <c r="K7" s="0" t="n">
+        <f aca="true" t="array" ref="K7">SUM((INDIRECT("D"&amp;ROW())-INDIRECT("C"&amp;ROW()))*2*24,(INDIRECT("F"&amp;ROW())-INDIRECT("E"&amp;ROW()))*2*24,(INDIRECT("H"&amp;ROW())-INDIRECT("G"&amp;ROW()))*2*24)</f>
+        <v>2.96666666666667</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="27" t="str">
-        <f t="shared" si="0"/>
+        <f aca="false">IF(B8&gt;0,PROPER(TEXT(B8,"dddd")),"")</f>
         <v>Domingo</v>
       </c>
-      <c r="B8" s="32">
+      <c r="B8" s="32" t="n">
         <v>46145</v>
       </c>
-      <c r="C8" s="33">
-        <v>0.37013888888888902</v>
-      </c>
-      <c r="D8" s="34">
-        <v>0.55208333333333304</v>
-      </c>
-      <c r="E8" s="33">
-        <v>0.70902777777777803</v>
-      </c>
-      <c r="F8" s="34">
-        <v>0.79513888888888895</v>
+      <c r="C8" s="33" t="n">
+        <v>0.370138888888889</v>
+      </c>
+      <c r="D8" s="34" t="n">
+        <v>0.552083333333333</v>
+      </c>
+      <c r="E8" s="33" t="n">
+        <v>0.709027777777778</v>
+      </c>
+      <c r="F8" s="34" t="n">
+        <v>0.795138888888889</v>
       </c>
       <c r="G8" s="33"/>
       <c r="H8" s="34"/>
-      <c r="I8" s="33">
-        <v>0.26805555555555599</v>
+      <c r="I8" s="33" t="n">
+        <v>0.268055555555556</v>
       </c>
       <c r="J8" s="31" t="s">
         <v>19</v>
       </c>
-      <c r="K8" t="e">
-        <f t="array" aca="1" ref="K8" ca="1">SUM((INDIRECT("D"&amp;ROW())-INDIRECT("C"&amp;ROW()))*2*24,(INDIRECT("F"&amp;ROW())-INDIRECT("E"&amp;ROW()))*2*24,(INDIRECT("H"&amp;ROW())-INDIRECT("G"&amp;ROW()))*2*24)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="9" spans="1:14" ht="18.75">
+      <c r="K8" s="0" t="n">
+        <f aca="true" t="array" ref="K8">SUM((INDIRECT("D"&amp;ROW())-INDIRECT("C"&amp;ROW()))*2*24,(INDIRECT("F"&amp;ROW())-INDIRECT("E"&amp;ROW()))*2*24,(INDIRECT("H"&amp;ROW())-INDIRECT("G"&amp;ROW()))*2*24)</f>
+        <v>12.8666666666667</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="27" t="str">
-        <f t="shared" si="0"/>
+        <f aca="false">IF(B9&gt;0,PROPER(TEXT(B9,"dddd")),"")</f>
         <v>Lunes</v>
       </c>
-      <c r="B9" s="28">
+      <c r="B9" s="28" t="n">
         <v>46146</v>
       </c>
-      <c r="C9" s="33">
-        <v>0.67777777777777803</v>
-      </c>
-      <c r="D9" s="34">
-        <v>0.76666666666666705</v>
+      <c r="C9" s="33" t="n">
+        <v>0.677777777777778</v>
+      </c>
+      <c r="D9" s="34" t="n">
+        <v>0.766666666666667</v>
       </c>
       <c r="E9" s="33"/>
       <c r="F9" s="34"/>
       <c r="G9" s="33"/>
       <c r="H9" s="34"/>
-      <c r="I9" s="33">
-        <v>8.8888888888888906E-2</v>
+      <c r="I9" s="33" t="n">
+        <v>0.0888888888888889</v>
       </c>
       <c r="J9" s="31" t="s">
         <v>20</v>
       </c>
-      <c r="K9" t="e">
-        <f t="array" aca="1" ref="K9" ca="1">SUM((INDIRECT("D"&amp;ROW())-INDIRECT("C"&amp;ROW()))*1.5*24,(INDIRECT("F"&amp;ROW())-INDIRECT("E"&amp;ROW()))*1.5*24,(INDIRECT("H"&amp;ROW())-INDIRECT("G"&amp;ROW()))*1.5*24)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14" ht="18.75">
+      <c r="K9" s="0" t="n">
+        <f aca="true" t="array" ref="K9">SUM((INDIRECT("D"&amp;ROW())-INDIRECT("C"&amp;ROW()))*1.5*24,(INDIRECT("F"&amp;ROW())-INDIRECT("E"&amp;ROW()))*1.5*24,(INDIRECT("H"&amp;ROW())-INDIRECT("G"&amp;ROW()))*1.5*24)</f>
+        <v>3.2</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="27" t="str">
-        <f t="shared" si="0"/>
+        <f aca="false">IF(B10&gt;0,PROPER(TEXT(B10,"dddd")),"")</f>
         <v>Martes</v>
       </c>
-      <c r="B10" s="32">
+      <c r="B10" s="32" t="n">
         <v>46147</v>
       </c>
-      <c r="C10" s="33">
-        <v>0.36666666666666697</v>
-      </c>
-      <c r="D10" s="34">
-        <v>0.45069444444444401</v>
+      <c r="C10" s="33" t="n">
+        <v>0.366666666666667</v>
+      </c>
+      <c r="D10" s="34" t="n">
+        <v>0.450694444444444</v>
       </c>
       <c r="E10" s="33"/>
       <c r="F10" s="34"/>
       <c r="G10" s="33"/>
       <c r="H10" s="34"/>
-      <c r="I10" s="33">
-        <v>8.4027777777777798E-2</v>
+      <c r="I10" s="33" t="n">
+        <v>0.0840277777777778</v>
       </c>
       <c r="J10" s="31" t="s">
         <v>20</v>
       </c>
-      <c r="K10" t="e">
-        <f t="array" aca="1" ref="K10" ca="1">SUM((INDIRECT("D"&amp;ROW())-INDIRECT("C"&amp;ROW()))*1.5*24,(INDIRECT("F"&amp;ROW())-INDIRECT("E"&amp;ROW()))*1.5*24,(INDIRECT("H"&amp;ROW())-INDIRECT("G"&amp;ROW()))*1.5*24)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="11" spans="1:14" ht="18.75">
+      <c r="K10" s="0" t="n">
+        <f aca="true" t="array" ref="K10">SUM((INDIRECT("D"&amp;ROW())-INDIRECT("C"&amp;ROW()))*1.5*24,(INDIRECT("F"&amp;ROW())-INDIRECT("E"&amp;ROW()))*1.5*24,(INDIRECT("H"&amp;ROW())-INDIRECT("G"&amp;ROW()))*1.5*24)</f>
+        <v>3.025</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="27" t="str">
-        <f t="shared" si="0"/>
+        <f aca="false">IF(B11&gt;0,PROPER(TEXT(B11,"dddd")),"")</f>
         <v>Miércoles</v>
       </c>
-      <c r="B11" s="32">
+      <c r="B11" s="32" t="n">
         <v>46148</v>
       </c>
-      <c r="C11" s="33">
-        <v>0.79861111111111105</v>
-      </c>
-      <c r="D11" s="34">
-        <v>0.88541666666666696</v>
+      <c r="C11" s="33" t="n">
+        <v>0.798611111111111</v>
+      </c>
+      <c r="D11" s="34" t="n">
+        <v>0.885416666666667</v>
       </c>
       <c r="E11" s="33"/>
       <c r="F11" s="34"/>
       <c r="G11" s="33"/>
       <c r="H11" s="34"/>
-      <c r="I11" s="35">
-        <v>8.6805555555555594E-2</v>
+      <c r="I11" s="35" t="n">
+        <v>0.0868055555555556</v>
       </c>
       <c r="J11" s="31" t="s">
         <v>21</v>
       </c>
-      <c r="K11" t="e">
-        <f t="array" aca="1" ref="K11" ca="1">SUM((INDIRECT("D"&amp;ROW())-INDIRECT("C"&amp;ROW()))*1.5*24,(INDIRECT("F"&amp;ROW())-INDIRECT("E"&amp;ROW()))*1.5*24,(INDIRECT("H"&amp;ROW())-INDIRECT("G"&amp;ROW()))*1.5*24)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="12" spans="1:14" ht="18.75">
+      <c r="K11" s="0" t="n">
+        <f aca="true" t="array" ref="K11">SUM((INDIRECT("D"&amp;ROW())-INDIRECT("C"&amp;ROW()))*1.5*24,(INDIRECT("F"&amp;ROW())-INDIRECT("E"&amp;ROW()))*1.5*24,(INDIRECT("H"&amp;ROW())-INDIRECT("G"&amp;ROW()))*1.5*24)</f>
+        <v>3.125</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="27" t="str">
-        <f t="shared" si="0"/>
+        <f aca="false">IF(B12&gt;0,PROPER(TEXT(B12,"dddd")),"")</f>
         <v>Jueves</v>
       </c>
-      <c r="B12" s="28">
+      <c r="B12" s="28" t="n">
         <v>46149</v>
       </c>
-      <c r="C12" s="33">
+      <c r="C12" s="33" t="n">
         <v>0.75</v>
       </c>
-      <c r="D12" s="34">
-        <v>0.84722222222222199</v>
+      <c r="D12" s="34" t="n">
+        <v>0.847222222222222</v>
       </c>
       <c r="E12" s="33"/>
       <c r="F12" s="34"/>
       <c r="G12" s="33"/>
       <c r="H12" s="34"/>
-      <c r="I12" s="36">
-        <v>9.7222222222222196E-2</v>
+      <c r="I12" s="36" t="n">
+        <v>0.0972222222222222</v>
       </c>
       <c r="J12" s="31" t="s">
         <v>22</v>
       </c>
-      <c r="K12" t="e">
-        <f t="array" aca="1" ref="K12" ca="1">SUM((INDIRECT("D"&amp;ROW())-INDIRECT("C"&amp;ROW()))*1.5*24,(INDIRECT("F"&amp;ROW())-INDIRECT("E"&amp;ROW()))*1.5*24,(INDIRECT("H"&amp;ROW())-INDIRECT("G"&amp;ROW()))*1.5*24)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="13" spans="1:14" ht="18.75">
+      <c r="K12" s="0" t="n">
+        <f aca="true" t="array" ref="K12">SUM((INDIRECT("D"&amp;ROW())-INDIRECT("C"&amp;ROW()))*1.5*24,(INDIRECT("F"&amp;ROW())-INDIRECT("E"&amp;ROW()))*1.5*24,(INDIRECT("H"&amp;ROW())-INDIRECT("G"&amp;ROW()))*1.5*24)</f>
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="27" t="str">
-        <f t="shared" si="0"/>
+        <f aca="false">IF(B13&gt;0,PROPER(TEXT(B13,"dddd")),"")</f>
         <v>Viernes</v>
       </c>
-      <c r="B13" s="32">
+      <c r="B13" s="32" t="n">
         <v>46150</v>
       </c>
       <c r="C13" s="33"/>
@@ -1323,21 +1351,21 @@
       <c r="F13" s="34"/>
       <c r="G13" s="33"/>
       <c r="H13" s="34"/>
-      <c r="I13" s="29">
+      <c r="I13" s="29" t="n">
         <v>0</v>
       </c>
       <c r="J13" s="31"/>
-      <c r="K13" t="e">
-        <f t="array" aca="1" ref="K13" ca="1">SUM((INDIRECT("D"&amp;ROW())-INDIRECT("C"&amp;ROW()))*1.5*24,(INDIRECT("F"&amp;ROW())-INDIRECT("E"&amp;ROW()))*1.5*24,(INDIRECT("H"&amp;ROW())-INDIRECT("G"&amp;ROW()))*1.5*24)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="14" spans="1:14" ht="18.75">
+      <c r="K13" s="0" t="n">
+        <f aca="true" t="array" ref="K13">SUM((INDIRECT("D"&amp;ROW())-INDIRECT("C"&amp;ROW()))*1.5*24,(INDIRECT("F"&amp;ROW())-INDIRECT("E"&amp;ROW()))*1.5*24,(INDIRECT("H"&amp;ROW())-INDIRECT("G"&amp;ROW()))*1.5*24)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="27" t="str">
-        <f t="shared" si="0"/>
+        <f aca="false">IF(B14&gt;0,PROPER(TEXT(B14,"dddd")),"")</f>
         <v>Sábado</v>
       </c>
-      <c r="B14" s="32">
+      <c r="B14" s="32" t="n">
         <v>46151</v>
       </c>
       <c r="C14" s="33"/>
@@ -1346,50 +1374,50 @@
       <c r="F14" s="34"/>
       <c r="G14" s="33"/>
       <c r="H14" s="34"/>
-      <c r="I14" s="33">
+      <c r="I14" s="33" t="n">
         <v>0</v>
       </c>
       <c r="J14" s="31"/>
-      <c r="K14" t="e">
-        <f t="array" aca="1" ref="K14" ca="1">SUM((INDIRECT("D"&amp;ROW())-INDIRECT("C"&amp;ROW()))*2*24,(INDIRECT("F"&amp;ROW())-INDIRECT("E"&amp;ROW()))*2*24,(INDIRECT("H"&amp;ROW())-INDIRECT("G"&amp;ROW()))*2*24)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="15" spans="1:14" ht="18.75">
+      <c r="K14" s="0" t="n">
+        <f aca="true" t="array" ref="K14">SUM((INDIRECT("D"&amp;ROW())-INDIRECT("C"&amp;ROW()))*2*24,(INDIRECT("F"&amp;ROW())-INDIRECT("E"&amp;ROW()))*2*24,(INDIRECT("H"&amp;ROW())-INDIRECT("G"&amp;ROW()))*2*24)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="27" t="str">
-        <f t="shared" si="0"/>
+        <f aca="false">IF(B15&gt;0,PROPER(TEXT(B15,"dddd")),"")</f>
         <v>Domingo</v>
       </c>
-      <c r="B15" s="28">
+      <c r="B15" s="28" t="n">
         <v>46152</v>
       </c>
-      <c r="C15" s="33">
-        <v>0.72708333333333297</v>
-      </c>
-      <c r="D15" s="34">
-        <v>0.81736111111111098</v>
+      <c r="C15" s="33" t="n">
+        <v>0.727083333333333</v>
+      </c>
+      <c r="D15" s="34" t="n">
+        <v>0.817361111111111</v>
       </c>
       <c r="E15" s="33"/>
       <c r="F15" s="34"/>
       <c r="G15" s="33"/>
       <c r="H15" s="34"/>
-      <c r="I15" s="33">
-        <v>9.0277777777777804E-2</v>
+      <c r="I15" s="33" t="n">
+        <v>0.0902777777777778</v>
       </c>
       <c r="J15" s="31" t="s">
         <v>23</v>
       </c>
-      <c r="K15" t="e">
-        <f t="array" aca="1" ref="K15" ca="1">SUM((INDIRECT("D"&amp;ROW())-INDIRECT("C"&amp;ROW()))*2*24,(INDIRECT("F"&amp;ROW())-INDIRECT("E"&amp;ROW()))*2*24,(INDIRECT("H"&amp;ROW())-INDIRECT("G"&amp;ROW()))*2*24)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="16" spans="1:14" ht="18.75">
+      <c r="K15" s="0" t="n">
+        <f aca="true" t="array" ref="K15">SUM((INDIRECT("D"&amp;ROW())-INDIRECT("C"&amp;ROW()))*2*24,(INDIRECT("F"&amp;ROW())-INDIRECT("E"&amp;ROW()))*2*24,(INDIRECT("H"&amp;ROW())-INDIRECT("G"&amp;ROW()))*2*24)</f>
+        <v>4.33333333333333</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="27" t="str">
-        <f t="shared" si="0"/>
+        <f aca="false">IF(B16&gt;0,PROPER(TEXT(B16,"dddd")),"")</f>
         <v>Lunes</v>
       </c>
-      <c r="B16" s="32">
+      <c r="B16" s="32" t="n">
         <v>46153</v>
       </c>
       <c r="C16" s="33"/>
@@ -1398,50 +1426,50 @@
       <c r="F16" s="34"/>
       <c r="G16" s="33"/>
       <c r="H16" s="34"/>
-      <c r="I16" s="33">
-        <f t="shared" ref="I16:I36" si="1">SUM(C16:H16)</f>
+      <c r="I16" s="33" t="n">
+        <f aca="false">SUM(C16:H16)</f>
         <v>0</v>
       </c>
       <c r="J16" s="31"/>
-      <c r="K16" t="e">
-        <f t="array" aca="1" ref="K16" ca="1">SUM((INDIRECT("D"&amp;ROW())-INDIRECT("C"&amp;ROW()))*1.5*24,(INDIRECT("F"&amp;ROW())-INDIRECT("E"&amp;ROW()))*1.5*24,(INDIRECT("H"&amp;ROW())-INDIRECT("G"&amp;ROW()))*1.5*24)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="17" spans="1:11" ht="18.75">
+      <c r="K16" s="0" t="n">
+        <f aca="true" t="array" ref="K16">SUM((INDIRECT("D"&amp;ROW())-INDIRECT("C"&amp;ROW()))*1.5*24,(INDIRECT("F"&amp;ROW())-INDIRECT("E"&amp;ROW()))*1.5*24,(INDIRECT("H"&amp;ROW())-INDIRECT("G"&amp;ROW()))*1.5*24)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="27" t="str">
-        <f t="shared" si="0"/>
+        <f aca="false">IF(B17&gt;0,PROPER(TEXT(B17,"dddd")),"")</f>
         <v>Martes</v>
       </c>
-      <c r="B17" s="32">
+      <c r="B17" s="32" t="n">
         <v>46154</v>
       </c>
-      <c r="C17" s="33">
+      <c r="C17" s="33" t="n">
         <v>0.375</v>
       </c>
-      <c r="D17" s="34">
-        <v>0.91666666666666696</v>
+      <c r="D17" s="34" t="n">
+        <v>0.916666666666667</v>
       </c>
       <c r="E17" s="33"/>
       <c r="F17" s="34"/>
       <c r="G17" s="33"/>
       <c r="H17" s="34"/>
-      <c r="I17" s="33">
-        <f>D17-C17</f>
-        <v>0.54166666666666696</v>
+      <c r="I17" s="33" t="n">
+        <f aca="false">D17-C17</f>
+        <v>0.541666666666667</v>
       </c>
       <c r="J17" s="31"/>
-      <c r="K17" t="e">
-        <f t="array" aca="1" ref="K17" ca="1">SUM((INDIRECT("D"&amp;ROW())-INDIRECT("C"&amp;ROW()))*1.5*24,(INDIRECT("F"&amp;ROW())-INDIRECT("E"&amp;ROW()))*1.5*24,(INDIRECT("H"&amp;ROW())-INDIRECT("G"&amp;ROW()))*1.5*24)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="18" spans="1:11" ht="18.75">
+      <c r="K17" s="0" t="n">
+        <f aca="true" t="array" ref="K17">SUM((INDIRECT("D"&amp;ROW())-INDIRECT("C"&amp;ROW()))*1.5*24,(INDIRECT("F"&amp;ROW())-INDIRECT("E"&amp;ROW()))*1.5*24,(INDIRECT("H"&amp;ROW())-INDIRECT("G"&amp;ROW()))*1.5*24)</f>
+        <v>19.5</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="27" t="str">
-        <f t="shared" si="0"/>
+        <f aca="false">IF(B18&gt;0,PROPER(TEXT(B18,"dddd")),"")</f>
         <v>Miércoles</v>
       </c>
-      <c r="B18" s="28">
+      <c r="B18" s="28" t="n">
         <v>46155</v>
       </c>
       <c r="C18" s="33"/>
@@ -1450,22 +1478,22 @@
       <c r="F18" s="34"/>
       <c r="G18" s="33"/>
       <c r="H18" s="34"/>
-      <c r="I18" s="33">
-        <f t="shared" si="1"/>
+      <c r="I18" s="33" t="n">
+        <f aca="false">SUM(C18:H18)</f>
         <v>0</v>
       </c>
       <c r="J18" s="31"/>
-      <c r="K18" t="e">
-        <f t="array" aca="1" ref="K18" ca="1">SUM((INDIRECT("D"&amp;ROW())-INDIRECT("C"&amp;ROW()))*1.5*24,(INDIRECT("F"&amp;ROW())-INDIRECT("E"&amp;ROW()))*1.5*24,(INDIRECT("H"&amp;ROW())-INDIRECT("G"&amp;ROW()))*1.5*24)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="19" spans="1:11" ht="18.75">
+      <c r="K18" s="0" t="n">
+        <f aca="true" t="array" ref="K18">SUM((INDIRECT("D"&amp;ROW())-INDIRECT("C"&amp;ROW()))*1.5*24,(INDIRECT("F"&amp;ROW())-INDIRECT("E"&amp;ROW()))*1.5*24,(INDIRECT("H"&amp;ROW())-INDIRECT("G"&amp;ROW()))*1.5*24)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="27" t="str">
-        <f t="shared" si="0"/>
+        <f aca="false">IF(B19&gt;0,PROPER(TEXT(B19,"dddd")),"")</f>
         <v>Jueves</v>
       </c>
-      <c r="B19" s="32">
+      <c r="B19" s="32" t="n">
         <v>46156</v>
       </c>
       <c r="C19" s="33"/>
@@ -1474,22 +1502,22 @@
       <c r="F19" s="34"/>
       <c r="G19" s="33"/>
       <c r="H19" s="34"/>
-      <c r="I19" s="33">
-        <f t="shared" si="1"/>
+      <c r="I19" s="33" t="n">
+        <f aca="false">SUM(C19:H19)</f>
         <v>0</v>
       </c>
       <c r="J19" s="31"/>
-      <c r="K19" t="e">
-        <f t="array" aca="1" ref="K19" ca="1">SUM((INDIRECT("D"&amp;ROW())-INDIRECT("C"&amp;ROW()))*1.5*24,(INDIRECT("F"&amp;ROW())-INDIRECT("E"&amp;ROW()))*1.5*24,(INDIRECT("H"&amp;ROW())-INDIRECT("G"&amp;ROW()))*1.5*24)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="20" spans="1:11" ht="18.75">
+      <c r="K19" s="0" t="n">
+        <f aca="true" t="array" ref="K19">SUM((INDIRECT("D"&amp;ROW())-INDIRECT("C"&amp;ROW()))*1.5*24,(INDIRECT("F"&amp;ROW())-INDIRECT("E"&amp;ROW()))*1.5*24,(INDIRECT("H"&amp;ROW())-INDIRECT("G"&amp;ROW()))*1.5*24)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="27" t="str">
-        <f t="shared" si="0"/>
+        <f aca="false">IF(B20&gt;0,PROPER(TEXT(B20,"dddd")),"")</f>
         <v>Viernes</v>
       </c>
-      <c r="B20" s="32">
+      <c r="B20" s="32" t="n">
         <v>46157</v>
       </c>
       <c r="C20" s="33"/>
@@ -1498,22 +1526,22 @@
       <c r="F20" s="34"/>
       <c r="G20" s="33"/>
       <c r="H20" s="34"/>
-      <c r="I20" s="33">
-        <f t="shared" si="1"/>
+      <c r="I20" s="33" t="n">
+        <f aca="false">SUM(C20:H20)</f>
         <v>0</v>
       </c>
       <c r="J20" s="31"/>
-      <c r="K20" t="e">
-        <f t="array" aca="1" ref="K20" ca="1">SUM((INDIRECT("D"&amp;ROW())-INDIRECT("C"&amp;ROW()))*1.5*24,(INDIRECT("F"&amp;ROW())-INDIRECT("E"&amp;ROW()))*1.5*24,(INDIRECT("H"&amp;ROW())-INDIRECT("G"&amp;ROW()))*1.5*24)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="21" spans="1:11" ht="18.75">
+      <c r="K20" s="0" t="n">
+        <f aca="true" t="array" ref="K20">SUM((INDIRECT("D"&amp;ROW())-INDIRECT("C"&amp;ROW()))*1.5*24,(INDIRECT("F"&amp;ROW())-INDIRECT("E"&amp;ROW()))*1.5*24,(INDIRECT("H"&amp;ROW())-INDIRECT("G"&amp;ROW()))*1.5*24)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="27" t="str">
-        <f t="shared" si="0"/>
+        <f aca="false">IF(B21&gt;0,PROPER(TEXT(B21,"dddd")),"")</f>
         <v>Sábado</v>
       </c>
-      <c r="B21" s="28">
+      <c r="B21" s="28" t="n">
         <v>46158</v>
       </c>
       <c r="C21" s="33"/>
@@ -1522,22 +1550,22 @@
       <c r="F21" s="34"/>
       <c r="G21" s="33"/>
       <c r="H21" s="34"/>
-      <c r="I21" s="33">
-        <f t="shared" si="1"/>
+      <c r="I21" s="33" t="n">
+        <f aca="false">SUM(C21:H21)</f>
         <v>0</v>
       </c>
       <c r="J21" s="31"/>
-      <c r="K21" t="e">
-        <f t="array" aca="1" ref="K21" ca="1">SUM((INDIRECT("D"&amp;ROW())-INDIRECT("C"&amp;ROW()))*2*24,(INDIRECT("F"&amp;ROW())-INDIRECT("E"&amp;ROW()))*2*24,(INDIRECT("H"&amp;ROW())-INDIRECT("G"&amp;ROW()))*2*24)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="22" spans="1:11" ht="18.75">
+      <c r="K21" s="0" t="n">
+        <f aca="true" t="array" ref="K21">SUM((INDIRECT("D"&amp;ROW())-INDIRECT("C"&amp;ROW()))*2*24,(INDIRECT("F"&amp;ROW())-INDIRECT("E"&amp;ROW()))*2*24,(INDIRECT("H"&amp;ROW())-INDIRECT("G"&amp;ROW()))*2*24)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="27" t="str">
-        <f t="shared" si="0"/>
+        <f aca="false">IF(B22&gt;0,PROPER(TEXT(B22,"dddd")),"")</f>
         <v>Domingo</v>
       </c>
-      <c r="B22" s="32">
+      <c r="B22" s="32" t="n">
         <v>46159</v>
       </c>
       <c r="C22" s="33"/>
@@ -1546,22 +1574,22 @@
       <c r="F22" s="34"/>
       <c r="G22" s="33"/>
       <c r="H22" s="34"/>
-      <c r="I22" s="33">
-        <f t="shared" si="1"/>
+      <c r="I22" s="33" t="n">
+        <f aca="false">SUM(C22:H22)</f>
         <v>0</v>
       </c>
       <c r="J22" s="31"/>
-      <c r="K22" t="e">
-        <f t="array" aca="1" ref="K22" ca="1">SUM((INDIRECT("D"&amp;ROW())-INDIRECT("C"&amp;ROW()))*2*24,(INDIRECT("F"&amp;ROW())-INDIRECT("E"&amp;ROW()))*2*24,(INDIRECT("H"&amp;ROW())-INDIRECT("G"&amp;ROW()))*2*24)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="23" spans="1:11" ht="18.75">
+      <c r="K22" s="0" t="n">
+        <f aca="true" t="array" ref="K22">SUM((INDIRECT("D"&amp;ROW())-INDIRECT("C"&amp;ROW()))*2*24,(INDIRECT("F"&amp;ROW())-INDIRECT("E"&amp;ROW()))*2*24,(INDIRECT("H"&amp;ROW())-INDIRECT("G"&amp;ROW()))*2*24)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="27" t="str">
-        <f t="shared" si="0"/>
+        <f aca="false">IF(B23&gt;0,PROPER(TEXT(B23,"dddd")),"")</f>
         <v>Lunes</v>
       </c>
-      <c r="B23" s="32">
+      <c r="B23" s="32" t="n">
         <v>46160</v>
       </c>
       <c r="C23" s="33"/>
@@ -1570,22 +1598,22 @@
       <c r="F23" s="34"/>
       <c r="G23" s="33"/>
       <c r="H23" s="34"/>
-      <c r="I23" s="33">
-        <f t="shared" si="1"/>
+      <c r="I23" s="33" t="n">
+        <f aca="false">SUM(C23:H23)</f>
         <v>0</v>
       </c>
       <c r="J23" s="31"/>
-      <c r="K23" t="e">
-        <f t="array" aca="1" ref="K23" ca="1">SUM((INDIRECT("D"&amp;ROW())-INDIRECT("C"&amp;ROW()))*1.5*24,(INDIRECT("F"&amp;ROW())-INDIRECT("E"&amp;ROW()))*1.5*24,(INDIRECT("H"&amp;ROW())-INDIRECT("G"&amp;ROW()))*1.5*24)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="24" spans="1:11" ht="18.75">
+      <c r="K23" s="0" t="n">
+        <f aca="true" t="array" ref="K23">SUM((INDIRECT("D"&amp;ROW())-INDIRECT("C"&amp;ROW()))*1.5*24,(INDIRECT("F"&amp;ROW())-INDIRECT("E"&amp;ROW()))*1.5*24,(INDIRECT("H"&amp;ROW())-INDIRECT("G"&amp;ROW()))*1.5*24)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="27" t="str">
-        <f t="shared" si="0"/>
+        <f aca="false">IF(B24&gt;0,PROPER(TEXT(B24,"dddd")),"")</f>
         <v>Martes</v>
       </c>
-      <c r="B24" s="28">
+      <c r="B24" s="28" t="n">
         <v>46161</v>
       </c>
       <c r="C24" s="33"/>
@@ -1594,22 +1622,22 @@
       <c r="F24" s="34"/>
       <c r="G24" s="33"/>
       <c r="H24" s="34"/>
-      <c r="I24" s="33">
-        <f t="shared" si="1"/>
+      <c r="I24" s="33" t="n">
+        <f aca="false">SUM(C24:H24)</f>
         <v>0</v>
       </c>
       <c r="J24" s="31"/>
-      <c r="K24" t="e">
-        <f t="array" aca="1" ref="K24" ca="1">SUM((INDIRECT("D"&amp;ROW())-INDIRECT("C"&amp;ROW()))*1.5*24,(INDIRECT("F"&amp;ROW())-INDIRECT("E"&amp;ROW()))*1.5*24,(INDIRECT("H"&amp;ROW())-INDIRECT("G"&amp;ROW()))*1.5*24)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="25" spans="1:11" ht="18.75">
+      <c r="K24" s="0" t="n">
+        <f aca="true" t="array" ref="K24">SUM((INDIRECT("D"&amp;ROW())-INDIRECT("C"&amp;ROW()))*1.5*24,(INDIRECT("F"&amp;ROW())-INDIRECT("E"&amp;ROW()))*1.5*24,(INDIRECT("H"&amp;ROW())-INDIRECT("G"&amp;ROW()))*1.5*24)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="27" t="str">
-        <f t="shared" si="0"/>
+        <f aca="false">IF(B25&gt;0,PROPER(TEXT(B25,"dddd")),"")</f>
         <v>Miércoles</v>
       </c>
-      <c r="B25" s="32">
+      <c r="B25" s="32" t="n">
         <v>46162</v>
       </c>
       <c r="C25" s="33"/>
@@ -1618,22 +1646,22 @@
       <c r="F25" s="34"/>
       <c r="G25" s="33"/>
       <c r="H25" s="34"/>
-      <c r="I25" s="33">
-        <f t="shared" si="1"/>
+      <c r="I25" s="33" t="n">
+        <f aca="false">SUM(C25:H25)</f>
         <v>0</v>
       </c>
       <c r="J25" s="31"/>
-      <c r="K25" t="e">
-        <f t="array" aca="1" ref="K25" ca="1">SUM((INDIRECT("D"&amp;ROW())-INDIRECT("C"&amp;ROW()))*1.5*24,(INDIRECT("F"&amp;ROW())-INDIRECT("E"&amp;ROW()))*1.5*24,(INDIRECT("H"&amp;ROW())-INDIRECT("G"&amp;ROW()))*1.5*24)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="26" spans="1:11" ht="18.75">
+      <c r="K25" s="0" t="n">
+        <f aca="true" t="array" ref="K25">SUM((INDIRECT("D"&amp;ROW())-INDIRECT("C"&amp;ROW()))*1.5*24,(INDIRECT("F"&amp;ROW())-INDIRECT("E"&amp;ROW()))*1.5*24,(INDIRECT("H"&amp;ROW())-INDIRECT("G"&amp;ROW()))*1.5*24)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="27" t="str">
-        <f t="shared" si="0"/>
+        <f aca="false">IF(B26&gt;0,PROPER(TEXT(B26,"dddd")),"")</f>
         <v>Jueves</v>
       </c>
-      <c r="B26" s="32">
+      <c r="B26" s="32" t="n">
         <v>46163</v>
       </c>
       <c r="C26" s="33"/>
@@ -1642,22 +1670,22 @@
       <c r="F26" s="34"/>
       <c r="G26" s="33"/>
       <c r="H26" s="34"/>
-      <c r="I26" s="33">
-        <f t="shared" si="1"/>
+      <c r="I26" s="33" t="n">
+        <f aca="false">SUM(C26:H26)</f>
         <v>0</v>
       </c>
       <c r="J26" s="31"/>
-      <c r="K26" t="e">
-        <f t="array" aca="1" ref="K26" ca="1">SUM((INDIRECT("D"&amp;ROW())-INDIRECT("C"&amp;ROW()))*1.5*24,(INDIRECT("F"&amp;ROW())-INDIRECT("E"&amp;ROW()))*1.5*24,(INDIRECT("H"&amp;ROW())-INDIRECT("G"&amp;ROW()))*1.5*24)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="27" spans="1:11" ht="18.75">
+      <c r="K26" s="0" t="n">
+        <f aca="true" t="array" ref="K26">SUM((INDIRECT("D"&amp;ROW())-INDIRECT("C"&amp;ROW()))*1.5*24,(INDIRECT("F"&amp;ROW())-INDIRECT("E"&amp;ROW()))*1.5*24,(INDIRECT("H"&amp;ROW())-INDIRECT("G"&amp;ROW()))*1.5*24)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="27" t="str">
-        <f t="shared" si="0"/>
+        <f aca="false">IF(B27&gt;0,PROPER(TEXT(B27,"dddd")),"")</f>
         <v>Viernes</v>
       </c>
-      <c r="B27" s="28">
+      <c r="B27" s="28" t="n">
         <v>46164</v>
       </c>
       <c r="C27" s="33"/>
@@ -1666,22 +1694,22 @@
       <c r="F27" s="34"/>
       <c r="G27" s="33"/>
       <c r="H27" s="34"/>
-      <c r="I27" s="33">
-        <f t="shared" si="1"/>
+      <c r="I27" s="33" t="n">
+        <f aca="false">SUM(C27:H27)</f>
         <v>0</v>
       </c>
       <c r="J27" s="31"/>
-      <c r="K27" t="e">
-        <f t="array" aca="1" ref="K27" ca="1">SUM((INDIRECT("D"&amp;ROW())-INDIRECT("C"&amp;ROW()))*1.5*24,(INDIRECT("F"&amp;ROW())-INDIRECT("E"&amp;ROW()))*1.5*24,(INDIRECT("H"&amp;ROW())-INDIRECT("G"&amp;ROW()))*1.5*24)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="28" spans="1:11" ht="18.75">
+      <c r="K27" s="0" t="n">
+        <f aca="true" t="array" ref="K27">SUM((INDIRECT("D"&amp;ROW())-INDIRECT("C"&amp;ROW()))*1.5*24,(INDIRECT("F"&amp;ROW())-INDIRECT("E"&amp;ROW()))*1.5*24,(INDIRECT("H"&amp;ROW())-INDIRECT("G"&amp;ROW()))*1.5*24)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="27" t="str">
-        <f t="shared" si="0"/>
+        <f aca="false">IF(B28&gt;0,PROPER(TEXT(B28,"dddd")),"")</f>
         <v>Sábado</v>
       </c>
-      <c r="B28" s="32">
+      <c r="B28" s="32" t="n">
         <v>46165</v>
       </c>
       <c r="C28" s="33"/>
@@ -1690,22 +1718,22 @@
       <c r="F28" s="34"/>
       <c r="G28" s="33"/>
       <c r="H28" s="34"/>
-      <c r="I28" s="33">
-        <f t="shared" si="1"/>
+      <c r="I28" s="33" t="n">
+        <f aca="false">SUM(C28:H28)</f>
         <v>0</v>
       </c>
       <c r="J28" s="31"/>
-      <c r="K28" t="e">
-        <f t="array" aca="1" ref="K28" ca="1">SUM((INDIRECT("D"&amp;ROW())-INDIRECT("C"&amp;ROW()))*2*24,(INDIRECT("F"&amp;ROW())-INDIRECT("E"&amp;ROW()))*2*24,(INDIRECT("H"&amp;ROW())-INDIRECT("G"&amp;ROW()))*2*24)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="29" spans="1:11" ht="18.75">
+      <c r="K28" s="0" t="n">
+        <f aca="true" t="array" ref="K28">SUM((INDIRECT("D"&amp;ROW())-INDIRECT("C"&amp;ROW()))*2*24,(INDIRECT("F"&amp;ROW())-INDIRECT("E"&amp;ROW()))*2*24,(INDIRECT("H"&amp;ROW())-INDIRECT("G"&amp;ROW()))*2*24)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="27" t="str">
-        <f t="shared" si="0"/>
+        <f aca="false">IF(B29&gt;0,PROPER(TEXT(B29,"dddd")),"")</f>
         <v>Domingo</v>
       </c>
-      <c r="B29" s="32">
+      <c r="B29" s="32" t="n">
         <v>46166</v>
       </c>
       <c r="C29" s="33"/>
@@ -1714,22 +1742,22 @@
       <c r="F29" s="34"/>
       <c r="G29" s="33"/>
       <c r="H29" s="34"/>
-      <c r="I29" s="33">
-        <f t="shared" si="1"/>
+      <c r="I29" s="33" t="n">
+        <f aca="false">SUM(C29:H29)</f>
         <v>0</v>
       </c>
       <c r="J29" s="31"/>
-      <c r="K29" t="e">
-        <f t="array" aca="1" ref="K29" ca="1">SUM((INDIRECT("D"&amp;ROW())-INDIRECT("C"&amp;ROW()))*2*24,(INDIRECT("F"&amp;ROW())-INDIRECT("E"&amp;ROW()))*2*24,(INDIRECT("H"&amp;ROW())-INDIRECT("G"&amp;ROW()))*2*24)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="30" spans="1:11" ht="18.75">
+      <c r="K29" s="0" t="n">
+        <f aca="true" t="array" ref="K29">SUM((INDIRECT("D"&amp;ROW())-INDIRECT("C"&amp;ROW()))*2*24,(INDIRECT("F"&amp;ROW())-INDIRECT("E"&amp;ROW()))*2*24,(INDIRECT("H"&amp;ROW())-INDIRECT("G"&amp;ROW()))*2*24)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="27" t="str">
-        <f t="shared" si="0"/>
+        <f aca="false">IF(B30&gt;0,PROPER(TEXT(B30,"dddd")),"")</f>
         <v>Lunes</v>
       </c>
-      <c r="B30" s="28">
+      <c r="B30" s="28" t="n">
         <v>46167</v>
       </c>
       <c r="C30" s="33"/>
@@ -1738,22 +1766,22 @@
       <c r="F30" s="34"/>
       <c r="G30" s="33"/>
       <c r="H30" s="34"/>
-      <c r="I30" s="33">
-        <f t="shared" si="1"/>
+      <c r="I30" s="33" t="n">
+        <f aca="false">SUM(C30:H30)</f>
         <v>0</v>
       </c>
       <c r="J30" s="31"/>
-      <c r="K30" t="e">
-        <f t="array" aca="1" ref="K30" ca="1">SUM((INDIRECT("D"&amp;ROW())-INDIRECT("C"&amp;ROW()))*2*24,(INDIRECT("F"&amp;ROW())-INDIRECT("E"&amp;ROW()))*2*24,(INDIRECT("H"&amp;ROW())-INDIRECT("G"&amp;ROW()))*2*24)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="31" spans="1:11" ht="18.75">
+      <c r="K30" s="0" t="n">
+        <f aca="true" t="array" ref="K30">SUM((INDIRECT("D"&amp;ROW())-INDIRECT("C"&amp;ROW()))*2*24,(INDIRECT("F"&amp;ROW())-INDIRECT("E"&amp;ROW()))*2*24,(INDIRECT("H"&amp;ROW())-INDIRECT("G"&amp;ROW()))*2*24)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="27" t="str">
-        <f t="shared" si="0"/>
+        <f aca="false">IF(B31&gt;0,PROPER(TEXT(B31,"dddd")),"")</f>
         <v>Martes</v>
       </c>
-      <c r="B31" s="32">
+      <c r="B31" s="32" t="n">
         <v>46168</v>
       </c>
       <c r="C31" s="33"/>
@@ -1762,22 +1790,22 @@
       <c r="F31" s="34"/>
       <c r="G31" s="33"/>
       <c r="H31" s="34"/>
-      <c r="I31" s="33">
-        <f t="shared" si="1"/>
+      <c r="I31" s="33" t="n">
+        <f aca="false">SUM(C31:H31)</f>
         <v>0</v>
       </c>
       <c r="J31" s="31"/>
-      <c r="K31" t="e">
-        <f t="array" aca="1" ref="K31" ca="1">SUM((INDIRECT("D"&amp;ROW())-INDIRECT("C"&amp;ROW()))*1.5*24,(INDIRECT("F"&amp;ROW())-INDIRECT("E"&amp;ROW()))*1.5*24,(INDIRECT("H"&amp;ROW())-INDIRECT("G"&amp;ROW()))*1.5*24)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="32" spans="1:11" ht="18.75">
+      <c r="K31" s="0" t="n">
+        <f aca="true" t="array" ref="K31">SUM((INDIRECT("D"&amp;ROW())-INDIRECT("C"&amp;ROW()))*1.5*24,(INDIRECT("F"&amp;ROW())-INDIRECT("E"&amp;ROW()))*1.5*24,(INDIRECT("H"&amp;ROW())-INDIRECT("G"&amp;ROW()))*1.5*24)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="27" t="str">
-        <f t="shared" si="0"/>
+        <f aca="false">IF(B32&gt;0,PROPER(TEXT(B32,"dddd")),"")</f>
         <v>Miércoles</v>
       </c>
-      <c r="B32" s="32">
+      <c r="B32" s="32" t="n">
         <v>46169</v>
       </c>
       <c r="C32" s="33"/>
@@ -1786,22 +1814,22 @@
       <c r="F32" s="34"/>
       <c r="G32" s="33"/>
       <c r="H32" s="34"/>
-      <c r="I32" s="33">
-        <f t="shared" si="1"/>
+      <c r="I32" s="33" t="n">
+        <f aca="false">SUM(C32:H32)</f>
         <v>0</v>
       </c>
       <c r="J32" s="31"/>
-      <c r="K32" t="e">
-        <f t="array" aca="1" ref="K32" ca="1">SUM((INDIRECT("D"&amp;ROW())-INDIRECT("C"&amp;ROW()))*1.5*24,(INDIRECT("F"&amp;ROW())-INDIRECT("E"&amp;ROW()))*1.5*24,(INDIRECT("H"&amp;ROW())-INDIRECT("G"&amp;ROW()))*1.5*24)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="33" spans="1:11" ht="18.75">
+      <c r="K32" s="0" t="n">
+        <f aca="true" t="array" ref="K32">SUM((INDIRECT("D"&amp;ROW())-INDIRECT("C"&amp;ROW()))*1.5*24,(INDIRECT("F"&amp;ROW())-INDIRECT("E"&amp;ROW()))*1.5*24,(INDIRECT("H"&amp;ROW())-INDIRECT("G"&amp;ROW()))*1.5*24)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="27" t="str">
-        <f t="shared" si="0"/>
+        <f aca="false">IF(B33&gt;0,PROPER(TEXT(B33,"dddd")),"")</f>
         <v>Jueves</v>
       </c>
-      <c r="B33" s="28">
+      <c r="B33" s="28" t="n">
         <v>46170</v>
       </c>
       <c r="C33" s="33"/>
@@ -1810,22 +1838,22 @@
       <c r="F33" s="34"/>
       <c r="G33" s="33"/>
       <c r="H33" s="34"/>
-      <c r="I33" s="33">
-        <f t="shared" si="1"/>
+      <c r="I33" s="33" t="n">
+        <f aca="false">SUM(C33:H33)</f>
         <v>0</v>
       </c>
       <c r="J33" s="31"/>
-      <c r="K33" t="e">
-        <f t="array" aca="1" ref="K33" ca="1">SUM((INDIRECT("D"&amp;ROW())-INDIRECT("C"&amp;ROW()))*1.5*24,(INDIRECT("F"&amp;ROW())-INDIRECT("E"&amp;ROW()))*1.5*24,(INDIRECT("H"&amp;ROW())-INDIRECT("G"&amp;ROW()))*1.5*24)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="34" spans="1:11" ht="18.75">
+      <c r="K33" s="0" t="n">
+        <f aca="true" t="array" ref="K33">SUM((INDIRECT("D"&amp;ROW())-INDIRECT("C"&amp;ROW()))*1.5*24,(INDIRECT("F"&amp;ROW())-INDIRECT("E"&amp;ROW()))*1.5*24,(INDIRECT("H"&amp;ROW())-INDIRECT("G"&amp;ROW()))*1.5*24)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="27" t="str">
-        <f t="shared" si="0"/>
+        <f aca="false">IF(B34&gt;0,PROPER(TEXT(B34,"dddd")),"")</f>
         <v>Viernes</v>
       </c>
-      <c r="B34" s="32">
+      <c r="B34" s="32" t="n">
         <v>46171</v>
       </c>
       <c r="C34" s="33"/>
@@ -1834,22 +1862,22 @@
       <c r="F34" s="34"/>
       <c r="G34" s="33"/>
       <c r="H34" s="34"/>
-      <c r="I34" s="33">
-        <f t="shared" si="1"/>
+      <c r="I34" s="33" t="n">
+        <f aca="false">SUM(C34:H34)</f>
         <v>0</v>
       </c>
       <c r="J34" s="31"/>
-      <c r="K34" t="e">
-        <f t="array" aca="1" ref="K34" ca="1">SUM((INDIRECT("D"&amp;ROW())-INDIRECT("C"&amp;ROW()))*1.5*24,(INDIRECT("F"&amp;ROW())-INDIRECT("E"&amp;ROW()))*1.5*24,(INDIRECT("H"&amp;ROW())-INDIRECT("G"&amp;ROW()))*1.5*24)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="35" spans="1:11" ht="18.75">
+      <c r="K34" s="0" t="n">
+        <f aca="true" t="array" ref="K34">SUM((INDIRECT("D"&amp;ROW())-INDIRECT("C"&amp;ROW()))*1.5*24,(INDIRECT("F"&amp;ROW())-INDIRECT("E"&amp;ROW()))*1.5*24,(INDIRECT("H"&amp;ROW())-INDIRECT("G"&amp;ROW()))*1.5*24)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="27" t="str">
-        <f t="shared" si="0"/>
+        <f aca="false">IF(B35&gt;0,PROPER(TEXT(B35,"dddd")),"")</f>
         <v>Sábado</v>
       </c>
-      <c r="B35" s="32">
+      <c r="B35" s="32" t="n">
         <v>46172</v>
       </c>
       <c r="C35" s="33"/>
@@ -1858,19 +1886,19 @@
       <c r="F35" s="34"/>
       <c r="G35" s="33"/>
       <c r="H35" s="34"/>
-      <c r="I35" s="33">
-        <f t="shared" si="1"/>
+      <c r="I35" s="33" t="n">
+        <f aca="false">SUM(C35:H35)</f>
         <v>0</v>
       </c>
       <c r="J35" s="31"/>
-      <c r="K35" t="e">
-        <f t="array" aca="1" ref="K35" ca="1">SUM((INDIRECT("D"&amp;ROW())-INDIRECT("C"&amp;ROW()))*2*24,(INDIRECT("F"&amp;ROW())-INDIRECT("E"&amp;ROW()))*2*24,(INDIRECT("H"&amp;ROW())-INDIRECT("G"&amp;ROW()))*2*24)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="36" spans="1:11" ht="18.75">
+      <c r="K35" s="0" t="n">
+        <f aca="true" t="array" ref="K35">SUM((INDIRECT("D"&amp;ROW())-INDIRECT("C"&amp;ROW()))*2*24,(INDIRECT("F"&amp;ROW())-INDIRECT("E"&amp;ROW()))*2*24,(INDIRECT("H"&amp;ROW())-INDIRECT("G"&amp;ROW()))*2*24)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="37" t="str">
-        <f t="shared" si="0"/>
+        <f aca="false">IF(B36&gt;0,PROPER(TEXT(B36,"dddd")),"")</f>
         <v/>
       </c>
       <c r="B36" s="38"/>
@@ -1880,13 +1908,13 @@
       <c r="F36" s="40"/>
       <c r="G36" s="39"/>
       <c r="H36" s="40"/>
-      <c r="I36" s="39">
-        <f t="shared" si="1"/>
+      <c r="I36" s="39" t="n">
+        <f aca="false">SUM(C36:H36)</f>
         <v>0</v>
       </c>
       <c r="J36" s="41"/>
     </row>
-    <row r="37" spans="1:11">
+    <row r="37" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="42"/>
       <c r="B37" s="43"/>
       <c r="C37" s="43"/>
@@ -1903,14 +1931,15 @@
     <mergeCell ref="A1:J1"/>
   </mergeCells>
   <conditionalFormatting sqref="I6:I36">
-    <cfRule type="cellIs" dxfId="1" priority="1" operator="equal">
+    <cfRule type="cellIs" priority="2" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <printOptions horizontalCentered="1"/>
-  <pageMargins left="0.27569444444444402" right="0.27569444444444402" top="0.23611111111111099" bottom="0.23611111111111099" header="0.511811023622047" footer="0.23611111111111099"/>
-  <pageSetup paperSize="9" scale="65" orientation="landscape" horizontalDpi="300" verticalDpi="300"/>
-  <headerFooter>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="true" verticalCentered="false"/>
+  <pageMargins left="0.275694444444444" right="0.275694444444444" top="0.236111111111111" bottom="0.236111111111111" header="0.511811023622047" footer="0.236111111111111"/>
+  <pageSetup paperSize="9" scale="65" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="landscape" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
     <oddFooter>&amp;RPágina &amp;P de &amp;N</oddFooter>
   </headerFooter>
   <drawing r:id="rId1"/>
